--- a/chromadb/docs/scholarship_qnas.xlsx
+++ b/chromadb/docs/scholarship_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\chromadb\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51734342-EFCE-4D24-BFA0-8655F6DBE5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C478917-77B9-4324-ACC9-BF13A1105333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -1086,9 +1086,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="65.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1096,7 +1099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1104,7 +1107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1112,7 +1115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1144,7 +1147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1152,7 +1155,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1160,7 +1163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1184,7 +1187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1200,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1208,7 +1211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1216,7 +1219,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1224,7 +1227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1256,7 +1259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -1280,7 +1283,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1296,7 +1299,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -1304,7 +1307,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -1312,7 +1315,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -1320,7 +1323,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -1336,7 +1339,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1344,7 +1347,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -1352,7 +1355,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -1360,7 +1363,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -1368,7 +1371,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>57</v>
       </c>
@@ -1376,7 +1379,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>59</v>
       </c>
@@ -1384,7 +1387,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -1392,7 +1395,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>63</v>
       </c>
@@ -1400,7 +1403,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1416,7 +1419,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -1424,7 +1427,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -1432,7 +1435,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>73</v>
       </c>

--- a/chromadb/docs/scholarship_qnas.xlsx
+++ b/chromadb/docs/scholarship_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\chromadb\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C478917-77B9-4324-ACC9-BF13A1105333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1737636C-B316-4E6A-A4B8-DB510394126D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
   <si>
     <t>Question</t>
   </si>
@@ -31,9 +31,6 @@
     <t>What are the scholarships available for me ?</t>
   </si>
   <si>
-    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.\n\nThe HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.\n\nThe Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements.</t>
-  </si>
-  <si>
     <t>What is the GPA requirement to maintain the Zell Miller Scholarship?</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t>What are the eligibility requirements for the HOPE Scholarship?</t>
   </si>
   <si>
-    <t>To qualify, you need to be a Georgia resident, have a 3.0 GPA in high school, and plan to attend an eligible Georgia postsecondary institution. See here for more information.</t>
-  </si>
-  <si>
     <t>qualify for Hope</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>What are the eligibility requirements for the Zell Miller Scholarship?</t>
   </si>
   <si>
-    <t>To qualify, you must be a Georgia resident, graduate high school with a 3.7 GPA, and have a score of at least 1200 on the SAT (combined Reading and Math) or 26 on the ACT. See here for more information.</t>
-  </si>
-  <si>
     <t>am I eligible for zell</t>
   </si>
   <si>
@@ -82,12 +73,6 @@
     <t>What is the GPA requirement to maintain the HOPE Scholarship?</t>
   </si>
   <si>
-    <t>To maintain the HOPE Scholarship, you need to maintain a cumulative GPA of 3.0 or higher once in</t>
-  </si>
-  <si>
-    <t>To maintain the Zell Miller Scholarship, you must maintain a cumulative GPA of 3.3 or higher once in</t>
-  </si>
-  <si>
     <t>Can I use the HOPE Scholarship for out-of-state colleges?</t>
   </si>
   <si>
@@ -106,9 +91,6 @@
     <t>How much money does the HOPE Scholarship provide?</t>
   </si>
   <si>
-    <t>The amount varies depending on the type of school (public or private) and other factors. For public colleges, it typically covers a portion of tuition, but students may still need additional funding for other</t>
-  </si>
-  <si>
     <t>How much money does the Zell Miller Scholarship provide?</t>
   </si>
   <si>
@@ -245,6 +227,27 @@
   </si>
   <si>
     <t>If you don’t meet the GPA requirement, you may lose the scholarship. However, you may be able to regain eligibility by improving your GPA in subsequent semesters.</t>
+  </si>
+  <si>
+    <t>scholarships</t>
+  </si>
+  <si>
+    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.\n\nThe HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.\n\nThe Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
+  </si>
+  <si>
+    <t>To qualify, you need to be a Georgia resident, have a 3.0 GPA in high school, and plan to attend an eligible Georgia postsecondary institution. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
+  </si>
+  <si>
+    <t>To qualify, you must be a Georgia resident, graduate high school with a 3.7 GPA, and have a score of at least 1200 on the SAT (combined Reading and Math) or 26 on the ACT. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
+  </si>
+  <si>
+    <t>To maintain the HOPE Scholarship, you need to maintain a cumulative GPA of 3.0 or higher once in college.</t>
+  </si>
+  <si>
+    <t>To maintain the Zell Miller Scholarship, you must maintain a cumulative GPA of 3.3 or higher once in college.</t>
+  </si>
+  <si>
+    <t>The amount varies depending on the type of school (public or private) and other factors. For public colleges, it typically covers a portion of tuition, but students may still need additional funding for other expenses.</t>
   </si>
 </sst>
 </file>
@@ -1104,343 +1107,343 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/chromadb/docs/scholarship_qnas.xlsx
+++ b/chromadb/docs/scholarship_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1737636C-B316-4E6A-A4B8-DB510394126D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A57290E-C6D5-4AB3-9CA9-DA636AF91FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/chromadb/docs/scholarship_qnas.xlsx
+++ b/chromadb/docs/scholarship_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A57290E-C6D5-4AB3-9CA9-DA636AF91FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46DC800-F698-44D0-AD73-A72E013690CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Question</t>
   </si>
@@ -49,27 +49,9 @@
     <t>What are the eligibility requirements for the HOPE Scholarship?</t>
   </si>
   <si>
-    <t>qualify for Hope</t>
-  </si>
-  <si>
-    <t>am I eligible for hope</t>
-  </si>
-  <si>
-    <t>gpa requirement for hope</t>
-  </si>
-  <si>
     <t>What are the eligibility requirements for the Zell Miller Scholarship?</t>
   </si>
   <si>
-    <t>am I eligible for zell</t>
-  </si>
-  <si>
-    <t>qualify for zell</t>
-  </si>
-  <si>
-    <t>gpa requirement for zell</t>
-  </si>
-  <si>
     <t>What is the GPA requirement to maintain the HOPE Scholarship?</t>
   </si>
   <si>
@@ -85,9 +67,6 @@
     <t>Like the HOPE Scholarship, the Zell Miller Scholarship can only be used at eligible Georgia institutions.</t>
   </si>
   <si>
-    <t>does zell cover out of state</t>
-  </si>
-  <si>
     <t>How much money does the HOPE Scholarship provide?</t>
   </si>
   <si>
@@ -103,18 +82,12 @@
     <t>To apply, complete the Free Application for Federal Student Aid (FAFSA) and the Georgia Student Finance Commission (GSFC) application for the HOPE Scholarship.</t>
   </si>
   <si>
-    <t>apply for hope</t>
-  </si>
-  <si>
     <t>How do I apply for the Zell Miller Scholarship?</t>
   </si>
   <si>
     <t>Similar to the HOPE Scholarship, you must complete the FAFSA and the Georgia Student Finance Commission (GSFC) application for the Zell Miller Scholarship.</t>
   </si>
   <si>
-    <t>apply for zell</t>
-  </si>
-  <si>
     <t>Is the HOPE Scholarship available to part-time students?</t>
   </si>
   <si>
@@ -145,9 +118,6 @@
     <t>If you lose the HOPE Scholarship due to a GPA drop, you may have a chance to regain it by improving your GPA in future semesters. Check with the Georgia Student Finance Commission (GSFC) for specific reinstatement requirements.</t>
   </si>
   <si>
-    <t>lose hope</t>
-  </si>
-  <si>
     <t>What happens if I lose my Zell Miller Scholarship?</t>
   </si>
   <si>
@@ -160,9 +130,6 @@
     <t>To maintain eligibility, you must enroll in at least 6 credit hours per semester, but full-time students are encouraged to take 12 or more credit hours.</t>
   </si>
   <si>
-    <t>hope credit</t>
-  </si>
-  <si>
     <t>How many credit hours can I take to keep the Zell Miller Scholarship?</t>
   </si>
   <si>
@@ -229,12 +196,6 @@
     <t>If you don’t meet the GPA requirement, you may lose the scholarship. However, you may be able to regain eligibility by improving your GPA in subsequent semesters.</t>
   </si>
   <si>
-    <t>scholarships</t>
-  </si>
-  <si>
-    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.\n\nThe HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.\n\nThe Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
-  </si>
-  <si>
     <t>To qualify, you need to be a Georgia resident, have a 3.0 GPA in high school, and plan to attend an eligible Georgia postsecondary institution. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
   </si>
   <si>
@@ -248,6 +209,9 @@
   </si>
   <si>
     <t>The amount varies depending on the type of school (public or private) and other factors. For public colleges, it typically covers a portion of tuition, but students may still need additional funding for other expenses.</t>
+  </si>
+  <si>
+    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.The HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.The Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.85546875" customWidth="1"/>
@@ -1107,55 +1071,55 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1163,287 +1127,191 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
         <v>57</v>
-      </c>
-      <c r="B39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>61</v>
-      </c>
-      <c r="B41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/chromadb/docs/scholarship_qnas.xlsx
+++ b/chromadb/docs/scholarship_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46DC800-F698-44D0-AD73-A72E013690CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31D51AA-5616-4DBD-A09B-E94C5ABA46E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/chromadb/docs/scholarship_qnas.xlsx
+++ b/chromadb/docs/scholarship_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31D51AA-5616-4DBD-A09B-E94C5ABA46E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF57213-9554-485C-A853-DA73AEEAF723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
   <si>
     <t>Question</t>
   </si>
@@ -212,6 +212,27 @@
   </si>
   <si>
     <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.The HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.The Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
+  </si>
+  <si>
+    <t>dual</t>
+  </si>
+  <si>
+    <t>Dual enrollment allows high school students to take college courses and earn both high school and college credit simultaneously.</t>
+  </si>
+  <si>
+    <t>academic standing</t>
+  </si>
+  <si>
+    <t>What's your Student ID ?</t>
+  </si>
+  <si>
+    <t>graduation</t>
+  </si>
+  <si>
+    <t>To graduate, you must complete a certain number of credits in required subjects (e.g., English, math, science, social studies), pass state exams, and fulfill any additional requirements set by your school.</t>
+  </si>
+  <si>
+    <t>graduation requirements</t>
   </si>
 </sst>
 </file>
@@ -1052,13 +1073,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.85546875" customWidth="1"/>
+    <col min="1" max="1" width="65.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1074,7 +1095,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1082,7 +1103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1090,7 +1111,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1098,7 +1119,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1106,7 +1127,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1114,7 +1135,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1122,7 +1143,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1130,7 +1151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1138,7 +1159,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1146,7 +1167,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1154,7 +1175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1162,7 +1183,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1170,7 +1191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1178,7 +1199,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1186,7 +1207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1194,7 +1215,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -1202,7 +1223,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1210,7 +1231,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1218,7 +1239,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1226,7 +1247,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1234,7 +1255,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -1242,7 +1263,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1250,7 +1271,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -1258,7 +1279,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -1266,7 +1287,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -1274,7 +1295,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -1282,7 +1303,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -1290,7 +1311,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -1298,7 +1319,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>54</v>
       </c>
@@ -1306,12 +1327,44 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>56</v>
       </c>
       <c r="B32" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/chromadb/docs/scholarship_qnas.xlsx
+++ b/chromadb/docs/scholarship_qnas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF57213-9554-485C-A853-DA73AEEAF723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865251B8-AC18-4A26-89E6-13F14FF7CE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
   <si>
     <t>Question</t>
   </si>
@@ -233,6 +233,21 @@
   </si>
   <si>
     <t>graduation requirements</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>AP classes are advanced courses that can help you prepare for college-level work. They are often more challenging, but they can improve your college applications and earn you college credit if you score well on the AP exams.</t>
+  </si>
+  <si>
+    <t>advanced courses</t>
+  </si>
+  <si>
+    <t>counselling</t>
+  </si>
+  <si>
+    <t>Sure, what do you want to know. You can ask things like bullying, FAFSA, SAT, ACT, college, etc.</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.81640625" customWidth="1"/>
@@ -1367,6 +1382,30 @@
         <v>69</v>
       </c>
     </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
